--- a/output/amazon_niche_rapor_2026-04-03.xlsx
+++ b/output/amazon_niche_rapor_2026-04-03.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -505,6 +505,34 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>metal arch backdrop stand and cover set</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>$55.63</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>70.6%</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-03.xlsx
+++ b/output/amazon_niche_rapor_2026-04-03.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -533,6 +533,34 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>garden trellis for climbing plants arch</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>$49.92</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>57.6%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-03.xlsx
+++ b/output/amazon_niche_rapor_2026-04-03.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,34 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>hp tuners mpvi4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>$224.85</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-03.xlsx
+++ b/output/amazon_niche_rapor_2026-04-03.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -589,6 +589,34 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>light hair removal devices</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>$184.11</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>45.8%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-03.xlsx
+++ b/output/amazon_niche_rapor_2026-04-03.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -617,6 +617,34 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>open arch backdrop stand</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>$60.38</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-03.xlsx
+++ b/output/amazon_niche_rapor_2026-04-03.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -645,6 +645,34 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>dewalt lawn edger cordless</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>$104.71</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>52.6%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-03.xlsx
+++ b/output/amazon_niche_rapor_2026-04-03.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -673,6 +673,34 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>wooden trellis arch outdoor</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>$56.09</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
